--- a/wwwroot/templates/AdjustmentTemplate.xlsx
+++ b/wwwroot/templates/AdjustmentTemplate.xlsx
@@ -8,16 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://daleuwuk.sharepoint.com/sites/Technology/Shared Documents/Prism/Reconciliations/Focus Group/Adjustments/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="59" documentId="8_{228C2430-AB2E-4A5F-9E85-F2D51C7E388C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9C9D017E-E542-4514-BA94-CFD24A64AB61}"/>
+  <xr:revisionPtr revIDLastSave="61" documentId="8_{228C2430-AB2E-4A5F-9E85-F2D51C7E388C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{ABC0A7B3-B5CD-4241-BBD9-913625E04EF3}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{784EC6A2-D110-4B3D-AC5F-01913A7C39E6}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{784EC6A2-D110-4B3D-AC5F-01913A7C39E6}"/>
   </bookViews>
   <sheets>
     <sheet name="Premium" sheetId="1" r:id="rId1"/>
     <sheet name="Recoveries" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Premium!$A$1:$O$17397</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Premium!$A$1:$P$17397</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Recoveries!$A$1:$R$2105</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="25">
   <si>
     <t>ORIPolicyReference</t>
   </si>
@@ -113,6 +113,9 @@
   </si>
   <si>
     <t>UltimateBasisRIPs</t>
+  </si>
+  <si>
+    <t>SignedPremium</t>
   </si>
 </sst>
 </file>
@@ -508,7 +511,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{49FDA544-07CD-40FE-921C-A333DF3D4537}">
-  <dimension ref="A1:O17339"/>
+  <dimension ref="A1:P17339"/>
   <sheetFormatPr defaultColWidth="9.28515625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="21.7109375" bestFit="1" customWidth="1"/>
@@ -520,24 +523,25 @@
     <col min="7" max="7" width="12.140625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="9.85546875" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="52.85546875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="20" style="3" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="19.28515625" style="3" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="20.42578125" style="3" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="19.85546875" style="3" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="28.5703125" style="3" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="28" style="3" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="26.140625" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="17.28515625" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="21.140625" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="21.28515625" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="11.28515625" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="15" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="15.140625" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="19.140625" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="52.85546875" customWidth="1"/>
+    <col min="11" max="11" width="20" style="3" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="19.28515625" style="3" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="20.42578125" style="3" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="19.85546875" style="3" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="28.5703125" style="3" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="28" style="3" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="26.140625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="17.28515625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="21.140625" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="21.28515625" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="15" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="15.140625" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="19.140625" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="13.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:16" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -565,703 +569,706 @@
       <c r="I1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="J1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="K1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="L1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="M1" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="N1" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="N1" s="2" t="s">
+      <c r="O1" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="O1" s="2" t="s">
+      <c r="P1" s="2" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="156" spans="10:11" x14ac:dyDescent="0.25">
-      <c r="J156" s="4"/>
+    <row r="156" spans="11:12" x14ac:dyDescent="0.25">
       <c r="K156" s="4"/>
-    </row>
-    <row r="175" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K175" s="4"/>
-    </row>
-    <row r="213" spans="10:11" x14ac:dyDescent="0.25">
-      <c r="J213" s="4"/>
+      <c r="L156" s="4"/>
+    </row>
+    <row r="175" spans="12:12" x14ac:dyDescent="0.25">
+      <c r="L175" s="4"/>
+    </row>
+    <row r="213" spans="11:12" x14ac:dyDescent="0.25">
       <c r="K213" s="4"/>
-    </row>
-    <row r="224" spans="10:11" x14ac:dyDescent="0.25">
-      <c r="J224" s="4"/>
+      <c r="L213" s="4"/>
+    </row>
+    <row r="224" spans="11:12" x14ac:dyDescent="0.25">
       <c r="K224" s="4"/>
-    </row>
-    <row r="295" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K295" s="4"/>
-    </row>
-    <row r="895" spans="12:13" x14ac:dyDescent="0.25">
-      <c r="L895" s="4"/>
+      <c r="L224" s="4"/>
+    </row>
+    <row r="295" spans="12:12" x14ac:dyDescent="0.25">
+      <c r="L295" s="4"/>
+    </row>
+    <row r="895" spans="13:14" x14ac:dyDescent="0.25">
       <c r="M895" s="4"/>
-    </row>
-    <row r="1143" spans="12:13" x14ac:dyDescent="0.25">
-      <c r="L1143" s="4"/>
+      <c r="N895" s="4"/>
+    </row>
+    <row r="1143" spans="13:14" x14ac:dyDescent="0.25">
       <c r="M1143" s="4"/>
-    </row>
-    <row r="1197" spans="10:11" x14ac:dyDescent="0.25">
-      <c r="J1197" s="4"/>
+      <c r="N1143" s="4"/>
+    </row>
+    <row r="1197" spans="11:12" x14ac:dyDescent="0.25">
       <c r="K1197" s="4"/>
-    </row>
-    <row r="1466" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K1466" s="4"/>
-    </row>
-    <row r="1482" spans="10:11" x14ac:dyDescent="0.25">
-      <c r="J1482" s="4"/>
+      <c r="L1197" s="4"/>
+    </row>
+    <row r="1466" spans="12:12" x14ac:dyDescent="0.25">
+      <c r="L1466" s="4"/>
+    </row>
+    <row r="1482" spans="11:12" x14ac:dyDescent="0.25">
       <c r="K1482" s="4"/>
-    </row>
-    <row r="1528" spans="10:11" x14ac:dyDescent="0.25">
-      <c r="J1528" s="4"/>
+      <c r="L1482" s="4"/>
+    </row>
+    <row r="1528" spans="11:12" x14ac:dyDescent="0.25">
       <c r="K1528" s="4"/>
-    </row>
-    <row r="1539" spans="10:11" x14ac:dyDescent="0.25">
-      <c r="J1539" s="4"/>
+      <c r="L1528" s="4"/>
+    </row>
+    <row r="1539" spans="11:12" x14ac:dyDescent="0.25">
       <c r="K1539" s="4"/>
-    </row>
-    <row r="1594" spans="10:11" x14ac:dyDescent="0.25">
-      <c r="J1594" s="4"/>
+      <c r="L1539" s="4"/>
+    </row>
+    <row r="1594" spans="11:12" x14ac:dyDescent="0.25">
       <c r="K1594" s="4"/>
-    </row>
-    <row r="1610" spans="10:11" x14ac:dyDescent="0.25">
-      <c r="J1610" s="4"/>
+      <c r="L1594" s="4"/>
+    </row>
+    <row r="1610" spans="11:12" x14ac:dyDescent="0.25">
       <c r="K1610" s="4"/>
-    </row>
-    <row r="1738" spans="10:11" x14ac:dyDescent="0.25">
-      <c r="J1738" s="4"/>
+      <c r="L1610" s="4"/>
+    </row>
+    <row r="1738" spans="11:12" x14ac:dyDescent="0.25">
       <c r="K1738" s="4"/>
-    </row>
-    <row r="1757" spans="10:11" x14ac:dyDescent="0.25">
-      <c r="J1757" s="4"/>
+      <c r="L1738" s="4"/>
+    </row>
+    <row r="1757" spans="11:12" x14ac:dyDescent="0.25">
       <c r="K1757" s="4"/>
-    </row>
-    <row r="1776" spans="10:11" x14ac:dyDescent="0.25">
-      <c r="J1776" s="4"/>
+      <c r="L1757" s="4"/>
+    </row>
+    <row r="1776" spans="11:12" x14ac:dyDescent="0.25">
       <c r="K1776" s="4"/>
-    </row>
-    <row r="2128" spans="10:11" x14ac:dyDescent="0.25">
-      <c r="J2128" s="4"/>
+      <c r="L1776" s="4"/>
+    </row>
+    <row r="2128" spans="11:12" x14ac:dyDescent="0.25">
       <c r="K2128" s="4"/>
-    </row>
-    <row r="2129" spans="10:11" x14ac:dyDescent="0.25">
-      <c r="J2129" s="4"/>
+      <c r="L2128" s="4"/>
+    </row>
+    <row r="2129" spans="11:12" x14ac:dyDescent="0.25">
       <c r="K2129" s="4"/>
-    </row>
-    <row r="2130" spans="10:11" x14ac:dyDescent="0.25">
-      <c r="J2130" s="4"/>
+      <c r="L2129" s="4"/>
+    </row>
+    <row r="2130" spans="11:12" x14ac:dyDescent="0.25">
       <c r="K2130" s="4"/>
-    </row>
-    <row r="2131" spans="10:11" x14ac:dyDescent="0.25">
-      <c r="J2131" s="4"/>
+      <c r="L2130" s="4"/>
+    </row>
+    <row r="2131" spans="11:12" x14ac:dyDescent="0.25">
       <c r="K2131" s="4"/>
-    </row>
-    <row r="2132" spans="10:11" x14ac:dyDescent="0.25">
-      <c r="J2132" s="4"/>
+      <c r="L2131" s="4"/>
+    </row>
+    <row r="2132" spans="11:12" x14ac:dyDescent="0.25">
       <c r="K2132" s="4"/>
-    </row>
-    <row r="2133" spans="10:11" x14ac:dyDescent="0.25">
-      <c r="J2133" s="4"/>
+      <c r="L2132" s="4"/>
+    </row>
+    <row r="2133" spans="11:12" x14ac:dyDescent="0.25">
       <c r="K2133" s="4"/>
-    </row>
-    <row r="2134" spans="10:11" x14ac:dyDescent="0.25">
-      <c r="J2134" s="4"/>
+      <c r="L2133" s="4"/>
+    </row>
+    <row r="2134" spans="11:12" x14ac:dyDescent="0.25">
       <c r="K2134" s="4"/>
-    </row>
-    <row r="2135" spans="10:11" x14ac:dyDescent="0.25">
-      <c r="J2135" s="4"/>
+      <c r="L2134" s="4"/>
+    </row>
+    <row r="2135" spans="11:12" x14ac:dyDescent="0.25">
       <c r="K2135" s="4"/>
-    </row>
-    <row r="2136" spans="10:11" x14ac:dyDescent="0.25">
-      <c r="J2136" s="4"/>
+      <c r="L2135" s="4"/>
+    </row>
+    <row r="2136" spans="11:12" x14ac:dyDescent="0.25">
       <c r="K2136" s="4"/>
-    </row>
-    <row r="2299" spans="10:11" x14ac:dyDescent="0.25">
-      <c r="J2299" s="4"/>
+      <c r="L2136" s="4"/>
+    </row>
+    <row r="2299" spans="11:12" x14ac:dyDescent="0.25">
       <c r="K2299" s="4"/>
-    </row>
-    <row r="2300" spans="10:11" x14ac:dyDescent="0.25">
-      <c r="J2300" s="4"/>
+      <c r="L2299" s="4"/>
+    </row>
+    <row r="2300" spans="11:12" x14ac:dyDescent="0.25">
       <c r="K2300" s="4"/>
-    </row>
-    <row r="2301" spans="10:11" x14ac:dyDescent="0.25">
-      <c r="J2301" s="4"/>
+      <c r="L2300" s="4"/>
+    </row>
+    <row r="2301" spans="11:12" x14ac:dyDescent="0.25">
       <c r="K2301" s="4"/>
-    </row>
-    <row r="2302" spans="10:11" x14ac:dyDescent="0.25">
-      <c r="J2302" s="4"/>
+      <c r="L2301" s="4"/>
+    </row>
+    <row r="2302" spans="11:12" x14ac:dyDescent="0.25">
       <c r="K2302" s="4"/>
-    </row>
-    <row r="2303" spans="10:11" x14ac:dyDescent="0.25">
-      <c r="J2303" s="4"/>
+      <c r="L2302" s="4"/>
+    </row>
+    <row r="2303" spans="11:12" x14ac:dyDescent="0.25">
       <c r="K2303" s="4"/>
-    </row>
-    <row r="2304" spans="10:11" x14ac:dyDescent="0.25">
-      <c r="J2304" s="4"/>
+      <c r="L2303" s="4"/>
+    </row>
+    <row r="2304" spans="11:12" x14ac:dyDescent="0.25">
       <c r="K2304" s="4"/>
-    </row>
-    <row r="2305" spans="10:11" x14ac:dyDescent="0.25">
-      <c r="J2305" s="4"/>
+      <c r="L2304" s="4"/>
+    </row>
+    <row r="2305" spans="11:12" x14ac:dyDescent="0.25">
       <c r="K2305" s="4"/>
-    </row>
-    <row r="2306" spans="10:11" x14ac:dyDescent="0.25">
-      <c r="J2306" s="4"/>
+      <c r="L2305" s="4"/>
+    </row>
+    <row r="2306" spans="11:12" x14ac:dyDescent="0.25">
       <c r="K2306" s="4"/>
-    </row>
-    <row r="2307" spans="10:11" x14ac:dyDescent="0.25">
-      <c r="J2307" s="4"/>
+      <c r="L2306" s="4"/>
+    </row>
+    <row r="2307" spans="11:12" x14ac:dyDescent="0.25">
       <c r="K2307" s="4"/>
-    </row>
-    <row r="2470" spans="10:11" x14ac:dyDescent="0.25">
-      <c r="J2470" s="4"/>
+      <c r="L2307" s="4"/>
+    </row>
+    <row r="2470" spans="11:12" x14ac:dyDescent="0.25">
       <c r="K2470" s="4"/>
-    </row>
-    <row r="2471" spans="10:11" x14ac:dyDescent="0.25">
-      <c r="J2471" s="4"/>
+      <c r="L2470" s="4"/>
+    </row>
+    <row r="2471" spans="11:12" x14ac:dyDescent="0.25">
       <c r="K2471" s="4"/>
-    </row>
-    <row r="2472" spans="10:11" x14ac:dyDescent="0.25">
-      <c r="J2472" s="4"/>
+      <c r="L2471" s="4"/>
+    </row>
+    <row r="2472" spans="11:12" x14ac:dyDescent="0.25">
       <c r="K2472" s="4"/>
-    </row>
-    <row r="2473" spans="10:11" x14ac:dyDescent="0.25">
-      <c r="J2473" s="4"/>
+      <c r="L2472" s="4"/>
+    </row>
+    <row r="2473" spans="11:12" x14ac:dyDescent="0.25">
       <c r="K2473" s="4"/>
-    </row>
-    <row r="2474" spans="10:11" x14ac:dyDescent="0.25">
-      <c r="J2474" s="4"/>
+      <c r="L2473" s="4"/>
+    </row>
+    <row r="2474" spans="11:12" x14ac:dyDescent="0.25">
       <c r="K2474" s="4"/>
-    </row>
-    <row r="2475" spans="10:11" x14ac:dyDescent="0.25">
-      <c r="J2475" s="4"/>
+      <c r="L2474" s="4"/>
+    </row>
+    <row r="2475" spans="11:12" x14ac:dyDescent="0.25">
       <c r="K2475" s="4"/>
-    </row>
-    <row r="2476" spans="10:11" x14ac:dyDescent="0.25">
-      <c r="J2476" s="4"/>
+      <c r="L2475" s="4"/>
+    </row>
+    <row r="2476" spans="11:12" x14ac:dyDescent="0.25">
       <c r="K2476" s="4"/>
-    </row>
-    <row r="2477" spans="10:11" x14ac:dyDescent="0.25">
-      <c r="J2477" s="4"/>
+      <c r="L2476" s="4"/>
+    </row>
+    <row r="2477" spans="11:12" x14ac:dyDescent="0.25">
       <c r="K2477" s="4"/>
-    </row>
-    <row r="2478" spans="10:11" x14ac:dyDescent="0.25">
-      <c r="J2478" s="4"/>
+      <c r="L2477" s="4"/>
+    </row>
+    <row r="2478" spans="11:12" x14ac:dyDescent="0.25">
       <c r="K2478" s="4"/>
-    </row>
-    <row r="2567" spans="10:11" x14ac:dyDescent="0.25">
-      <c r="J2567" s="4"/>
+      <c r="L2478" s="4"/>
+    </row>
+    <row r="2567" spans="11:12" x14ac:dyDescent="0.25">
       <c r="K2567" s="4"/>
-    </row>
-    <row r="2568" spans="10:11" x14ac:dyDescent="0.25">
-      <c r="J2568" s="4"/>
+      <c r="L2567" s="4"/>
+    </row>
+    <row r="2568" spans="11:12" x14ac:dyDescent="0.25">
       <c r="K2568" s="4"/>
-    </row>
-    <row r="2569" spans="10:11" x14ac:dyDescent="0.25">
-      <c r="J2569" s="4"/>
+      <c r="L2568" s="4"/>
+    </row>
+    <row r="2569" spans="11:12" x14ac:dyDescent="0.25">
       <c r="K2569" s="4"/>
-    </row>
-    <row r="2570" spans="10:11" x14ac:dyDescent="0.25">
-      <c r="J2570" s="4"/>
+      <c r="L2569" s="4"/>
+    </row>
+    <row r="2570" spans="11:12" x14ac:dyDescent="0.25">
       <c r="K2570" s="4"/>
-    </row>
-    <row r="2571" spans="10:11" x14ac:dyDescent="0.25">
-      <c r="J2571" s="4"/>
+      <c r="L2570" s="4"/>
+    </row>
+    <row r="2571" spans="11:12" x14ac:dyDescent="0.25">
       <c r="K2571" s="4"/>
-    </row>
-    <row r="2572" spans="10:11" x14ac:dyDescent="0.25">
-      <c r="J2572" s="4"/>
+      <c r="L2571" s="4"/>
+    </row>
+    <row r="2572" spans="11:12" x14ac:dyDescent="0.25">
       <c r="K2572" s="4"/>
-    </row>
-    <row r="2573" spans="10:11" x14ac:dyDescent="0.25">
-      <c r="J2573" s="4"/>
+      <c r="L2572" s="4"/>
+    </row>
+    <row r="2573" spans="11:12" x14ac:dyDescent="0.25">
       <c r="K2573" s="4"/>
-    </row>
-    <row r="2574" spans="10:11" x14ac:dyDescent="0.25">
-      <c r="J2574" s="4"/>
+      <c r="L2573" s="4"/>
+    </row>
+    <row r="2574" spans="11:12" x14ac:dyDescent="0.25">
       <c r="K2574" s="4"/>
-    </row>
-    <row r="2655" spans="10:11" x14ac:dyDescent="0.25">
-      <c r="J2655" s="4"/>
+      <c r="L2574" s="4"/>
+    </row>
+    <row r="2655" spans="11:12" x14ac:dyDescent="0.25">
       <c r="K2655" s="4"/>
-    </row>
-    <row r="2656" spans="10:11" x14ac:dyDescent="0.25">
-      <c r="J2656" s="4"/>
+      <c r="L2655" s="4"/>
+    </row>
+    <row r="2656" spans="11:12" x14ac:dyDescent="0.25">
       <c r="K2656" s="4"/>
-    </row>
-    <row r="2657" spans="10:11" x14ac:dyDescent="0.25">
-      <c r="J2657" s="4"/>
+      <c r="L2656" s="4"/>
+    </row>
+    <row r="2657" spans="11:12" x14ac:dyDescent="0.25">
       <c r="K2657" s="4"/>
-    </row>
-    <row r="2658" spans="10:11" x14ac:dyDescent="0.25">
-      <c r="J2658" s="4"/>
+      <c r="L2657" s="4"/>
+    </row>
+    <row r="2658" spans="11:12" x14ac:dyDescent="0.25">
       <c r="K2658" s="4"/>
-    </row>
-    <row r="2659" spans="10:11" x14ac:dyDescent="0.25">
-      <c r="J2659" s="4"/>
+      <c r="L2658" s="4"/>
+    </row>
+    <row r="2659" spans="11:12" x14ac:dyDescent="0.25">
       <c r="K2659" s="4"/>
-    </row>
-    <row r="2660" spans="10:11" x14ac:dyDescent="0.25">
-      <c r="J2660" s="4"/>
+      <c r="L2659" s="4"/>
+    </row>
+    <row r="2660" spans="11:12" x14ac:dyDescent="0.25">
       <c r="K2660" s="4"/>
-    </row>
-    <row r="2661" spans="10:11" x14ac:dyDescent="0.25">
-      <c r="J2661" s="4"/>
+      <c r="L2660" s="4"/>
+    </row>
+    <row r="2661" spans="11:12" x14ac:dyDescent="0.25">
       <c r="K2661" s="4"/>
-    </row>
-    <row r="2662" spans="10:11" x14ac:dyDescent="0.25">
-      <c r="J2662" s="4"/>
+      <c r="L2661" s="4"/>
+    </row>
+    <row r="2662" spans="11:12" x14ac:dyDescent="0.25">
       <c r="K2662" s="4"/>
-    </row>
-    <row r="2743" spans="10:11" x14ac:dyDescent="0.25">
-      <c r="J2743" s="4"/>
+      <c r="L2662" s="4"/>
+    </row>
+    <row r="2743" spans="11:12" x14ac:dyDescent="0.25">
       <c r="K2743" s="4"/>
-    </row>
-    <row r="2744" spans="10:11" x14ac:dyDescent="0.25">
-      <c r="J2744" s="4"/>
+      <c r="L2743" s="4"/>
+    </row>
+    <row r="2744" spans="11:12" x14ac:dyDescent="0.25">
       <c r="K2744" s="4"/>
-    </row>
-    <row r="2745" spans="10:11" x14ac:dyDescent="0.25">
-      <c r="J2745" s="4"/>
+      <c r="L2744" s="4"/>
+    </row>
+    <row r="2745" spans="11:12" x14ac:dyDescent="0.25">
       <c r="K2745" s="4"/>
-    </row>
-    <row r="2746" spans="10:11" x14ac:dyDescent="0.25">
-      <c r="J2746" s="4"/>
+      <c r="L2745" s="4"/>
+    </row>
+    <row r="2746" spans="11:12" x14ac:dyDescent="0.25">
       <c r="K2746" s="4"/>
-    </row>
-    <row r="2747" spans="10:11" x14ac:dyDescent="0.25">
-      <c r="J2747" s="4"/>
+      <c r="L2746" s="4"/>
+    </row>
+    <row r="2747" spans="11:12" x14ac:dyDescent="0.25">
       <c r="K2747" s="4"/>
-    </row>
-    <row r="2748" spans="10:11" x14ac:dyDescent="0.25">
-      <c r="J2748" s="4"/>
+      <c r="L2747" s="4"/>
+    </row>
+    <row r="2748" spans="11:12" x14ac:dyDescent="0.25">
       <c r="K2748" s="4"/>
-    </row>
-    <row r="2749" spans="10:11" x14ac:dyDescent="0.25">
-      <c r="J2749" s="4"/>
+      <c r="L2748" s="4"/>
+    </row>
+    <row r="2749" spans="11:12" x14ac:dyDescent="0.25">
       <c r="K2749" s="4"/>
-    </row>
-    <row r="2750" spans="10:11" x14ac:dyDescent="0.25">
-      <c r="J2750" s="4"/>
+      <c r="L2749" s="4"/>
+    </row>
+    <row r="2750" spans="11:12" x14ac:dyDescent="0.25">
       <c r="K2750" s="4"/>
-    </row>
-    <row r="2831" spans="10:11" x14ac:dyDescent="0.25">
-      <c r="J2831" s="4"/>
+      <c r="L2750" s="4"/>
+    </row>
+    <row r="2831" spans="11:12" x14ac:dyDescent="0.25">
       <c r="K2831" s="4"/>
-    </row>
-    <row r="2832" spans="10:11" x14ac:dyDescent="0.25">
-      <c r="J2832" s="4"/>
+      <c r="L2831" s="4"/>
+    </row>
+    <row r="2832" spans="11:12" x14ac:dyDescent="0.25">
       <c r="K2832" s="4"/>
-    </row>
-    <row r="2833" spans="10:11" x14ac:dyDescent="0.25">
-      <c r="J2833" s="4"/>
+      <c r="L2832" s="4"/>
+    </row>
+    <row r="2833" spans="11:12" x14ac:dyDescent="0.25">
       <c r="K2833" s="4"/>
-    </row>
-    <row r="2834" spans="10:11" x14ac:dyDescent="0.25">
-      <c r="J2834" s="4"/>
+      <c r="L2833" s="4"/>
+    </row>
+    <row r="2834" spans="11:12" x14ac:dyDescent="0.25">
       <c r="K2834" s="4"/>
-    </row>
-    <row r="2835" spans="10:11" x14ac:dyDescent="0.25">
-      <c r="J2835" s="4"/>
+      <c r="L2834" s="4"/>
+    </row>
+    <row r="2835" spans="11:12" x14ac:dyDescent="0.25">
       <c r="K2835" s="4"/>
-    </row>
-    <row r="2836" spans="10:11" x14ac:dyDescent="0.25">
-      <c r="J2836" s="4"/>
+      <c r="L2835" s="4"/>
+    </row>
+    <row r="2836" spans="11:12" x14ac:dyDescent="0.25">
       <c r="K2836" s="4"/>
-    </row>
-    <row r="2837" spans="10:11" x14ac:dyDescent="0.25">
-      <c r="J2837" s="4"/>
+      <c r="L2836" s="4"/>
+    </row>
+    <row r="2837" spans="11:12" x14ac:dyDescent="0.25">
       <c r="K2837" s="4"/>
-    </row>
-    <row r="2838" spans="10:11" x14ac:dyDescent="0.25">
-      <c r="J2838" s="4"/>
+      <c r="L2837" s="4"/>
+    </row>
+    <row r="2838" spans="11:12" x14ac:dyDescent="0.25">
       <c r="K2838" s="4"/>
-    </row>
-    <row r="2919" spans="10:11" x14ac:dyDescent="0.25">
-      <c r="J2919" s="4"/>
+      <c r="L2838" s="4"/>
+    </row>
+    <row r="2919" spans="11:12" x14ac:dyDescent="0.25">
       <c r="K2919" s="4"/>
-    </row>
-    <row r="2920" spans="10:11" x14ac:dyDescent="0.25">
-      <c r="J2920" s="4"/>
+      <c r="L2919" s="4"/>
+    </row>
+    <row r="2920" spans="11:12" x14ac:dyDescent="0.25">
       <c r="K2920" s="4"/>
-    </row>
-    <row r="2921" spans="10:11" x14ac:dyDescent="0.25">
-      <c r="J2921" s="4"/>
+      <c r="L2920" s="4"/>
+    </row>
+    <row r="2921" spans="11:12" x14ac:dyDescent="0.25">
       <c r="K2921" s="4"/>
-    </row>
-    <row r="2922" spans="10:11" x14ac:dyDescent="0.25">
-      <c r="J2922" s="4"/>
+      <c r="L2921" s="4"/>
+    </row>
+    <row r="2922" spans="11:12" x14ac:dyDescent="0.25">
       <c r="K2922" s="4"/>
-    </row>
-    <row r="2923" spans="10:11" x14ac:dyDescent="0.25">
-      <c r="J2923" s="4"/>
+      <c r="L2922" s="4"/>
+    </row>
+    <row r="2923" spans="11:12" x14ac:dyDescent="0.25">
       <c r="K2923" s="4"/>
-    </row>
-    <row r="2924" spans="10:11" x14ac:dyDescent="0.25">
-      <c r="J2924" s="4"/>
+      <c r="L2923" s="4"/>
+    </row>
+    <row r="2924" spans="11:12" x14ac:dyDescent="0.25">
       <c r="K2924" s="4"/>
-    </row>
-    <row r="2925" spans="10:11" x14ac:dyDescent="0.25">
-      <c r="J2925" s="4"/>
+      <c r="L2924" s="4"/>
+    </row>
+    <row r="2925" spans="11:12" x14ac:dyDescent="0.25">
       <c r="K2925" s="4"/>
-    </row>
-    <row r="2926" spans="10:11" x14ac:dyDescent="0.25">
-      <c r="J2926" s="4"/>
+      <c r="L2925" s="4"/>
+    </row>
+    <row r="2926" spans="11:12" x14ac:dyDescent="0.25">
       <c r="K2926" s="4"/>
-    </row>
-    <row r="3007" spans="10:11" x14ac:dyDescent="0.25">
-      <c r="J3007" s="4"/>
+      <c r="L2926" s="4"/>
+    </row>
+    <row r="3007" spans="11:12" x14ac:dyDescent="0.25">
       <c r="K3007" s="4"/>
-    </row>
-    <row r="3008" spans="10:11" x14ac:dyDescent="0.25">
-      <c r="J3008" s="4"/>
+      <c r="L3007" s="4"/>
+    </row>
+    <row r="3008" spans="11:12" x14ac:dyDescent="0.25">
       <c r="K3008" s="4"/>
-    </row>
-    <row r="3009" spans="10:11" x14ac:dyDescent="0.25">
-      <c r="J3009" s="4"/>
+      <c r="L3008" s="4"/>
+    </row>
+    <row r="3009" spans="11:12" x14ac:dyDescent="0.25">
       <c r="K3009" s="4"/>
-    </row>
-    <row r="3010" spans="10:11" x14ac:dyDescent="0.25">
-      <c r="J3010" s="4"/>
+      <c r="L3009" s="4"/>
+    </row>
+    <row r="3010" spans="11:12" x14ac:dyDescent="0.25">
       <c r="K3010" s="4"/>
-    </row>
-    <row r="3011" spans="10:11" x14ac:dyDescent="0.25">
-      <c r="J3011" s="4"/>
+      <c r="L3010" s="4"/>
+    </row>
+    <row r="3011" spans="11:12" x14ac:dyDescent="0.25">
       <c r="K3011" s="4"/>
-    </row>
-    <row r="3012" spans="10:11" x14ac:dyDescent="0.25">
-      <c r="J3012" s="4"/>
+      <c r="L3011" s="4"/>
+    </row>
+    <row r="3012" spans="11:12" x14ac:dyDescent="0.25">
       <c r="K3012" s="4"/>
-    </row>
-    <row r="3013" spans="10:11" x14ac:dyDescent="0.25">
-      <c r="J3013" s="4"/>
+      <c r="L3012" s="4"/>
+    </row>
+    <row r="3013" spans="11:12" x14ac:dyDescent="0.25">
       <c r="K3013" s="4"/>
-    </row>
-    <row r="3014" spans="10:11" x14ac:dyDescent="0.25">
-      <c r="J3014" s="4"/>
+      <c r="L3013" s="4"/>
+    </row>
+    <row r="3014" spans="11:12" x14ac:dyDescent="0.25">
       <c r="K3014" s="4"/>
-    </row>
-    <row r="3095" spans="10:11" x14ac:dyDescent="0.25">
-      <c r="J3095" s="4"/>
+      <c r="L3014" s="4"/>
+    </row>
+    <row r="3095" spans="11:12" x14ac:dyDescent="0.25">
       <c r="K3095" s="4"/>
-    </row>
-    <row r="3096" spans="10:11" x14ac:dyDescent="0.25">
-      <c r="J3096" s="4"/>
+      <c r="L3095" s="4"/>
+    </row>
+    <row r="3096" spans="11:12" x14ac:dyDescent="0.25">
       <c r="K3096" s="4"/>
-    </row>
-    <row r="3097" spans="10:11" x14ac:dyDescent="0.25">
-      <c r="J3097" s="4"/>
+      <c r="L3096" s="4"/>
+    </row>
+    <row r="3097" spans="11:12" x14ac:dyDescent="0.25">
       <c r="K3097" s="4"/>
-    </row>
-    <row r="3098" spans="10:11" x14ac:dyDescent="0.25">
-      <c r="J3098" s="4"/>
+      <c r="L3097" s="4"/>
+    </row>
+    <row r="3098" spans="11:12" x14ac:dyDescent="0.25">
       <c r="K3098" s="4"/>
-    </row>
-    <row r="3099" spans="10:11" x14ac:dyDescent="0.25">
-      <c r="J3099" s="4"/>
+      <c r="L3098" s="4"/>
+    </row>
+    <row r="3099" spans="11:12" x14ac:dyDescent="0.25">
       <c r="K3099" s="4"/>
-    </row>
-    <row r="3100" spans="10:11" x14ac:dyDescent="0.25">
-      <c r="J3100" s="4"/>
+      <c r="L3099" s="4"/>
+    </row>
+    <row r="3100" spans="11:12" x14ac:dyDescent="0.25">
       <c r="K3100" s="4"/>
-    </row>
-    <row r="3101" spans="10:11" x14ac:dyDescent="0.25">
-      <c r="J3101" s="4"/>
+      <c r="L3100" s="4"/>
+    </row>
+    <row r="3101" spans="11:12" x14ac:dyDescent="0.25">
       <c r="K3101" s="4"/>
-    </row>
-    <row r="3102" spans="10:11" x14ac:dyDescent="0.25">
-      <c r="J3102" s="4"/>
+      <c r="L3101" s="4"/>
+    </row>
+    <row r="3102" spans="11:12" x14ac:dyDescent="0.25">
       <c r="K3102" s="4"/>
-    </row>
-    <row r="3271" spans="10:11" x14ac:dyDescent="0.25">
-      <c r="J3271" s="4"/>
+      <c r="L3102" s="4"/>
+    </row>
+    <row r="3271" spans="11:12" x14ac:dyDescent="0.25">
       <c r="K3271" s="4"/>
-    </row>
-    <row r="3272" spans="10:11" x14ac:dyDescent="0.25">
-      <c r="J3272" s="4"/>
+      <c r="L3271" s="4"/>
+    </row>
+    <row r="3272" spans="11:12" x14ac:dyDescent="0.25">
       <c r="K3272" s="4"/>
-    </row>
-    <row r="3273" spans="10:11" x14ac:dyDescent="0.25">
-      <c r="J3273" s="4"/>
+      <c r="L3272" s="4"/>
+    </row>
+    <row r="3273" spans="11:12" x14ac:dyDescent="0.25">
       <c r="K3273" s="4"/>
-    </row>
-    <row r="3274" spans="10:11" x14ac:dyDescent="0.25">
-      <c r="J3274" s="4"/>
+      <c r="L3273" s="4"/>
+    </row>
+    <row r="3274" spans="11:12" x14ac:dyDescent="0.25">
       <c r="K3274" s="4"/>
-    </row>
-    <row r="3275" spans="10:11" x14ac:dyDescent="0.25">
-      <c r="J3275" s="4"/>
+      <c r="L3274" s="4"/>
+    </row>
+    <row r="3275" spans="11:12" x14ac:dyDescent="0.25">
       <c r="K3275" s="4"/>
-    </row>
-    <row r="3276" spans="10:11" x14ac:dyDescent="0.25">
-      <c r="J3276" s="4"/>
+      <c r="L3275" s="4"/>
+    </row>
+    <row r="3276" spans="11:12" x14ac:dyDescent="0.25">
       <c r="K3276" s="4"/>
-    </row>
-    <row r="3277" spans="10:11" x14ac:dyDescent="0.25">
-      <c r="J3277" s="4"/>
+      <c r="L3276" s="4"/>
+    </row>
+    <row r="3277" spans="11:12" x14ac:dyDescent="0.25">
       <c r="K3277" s="4"/>
-    </row>
-    <row r="3278" spans="10:11" x14ac:dyDescent="0.25">
-      <c r="J3278" s="4"/>
+      <c r="L3277" s="4"/>
+    </row>
+    <row r="3278" spans="11:12" x14ac:dyDescent="0.25">
       <c r="K3278" s="4"/>
-    </row>
-    <row r="4216" spans="10:11" x14ac:dyDescent="0.25">
-      <c r="J4216" s="4"/>
+      <c r="L3278" s="4"/>
+    </row>
+    <row r="4216" spans="11:12" x14ac:dyDescent="0.25">
       <c r="K4216" s="4"/>
-    </row>
-    <row r="4227" spans="10:11" x14ac:dyDescent="0.25">
-      <c r="J4227" s="4"/>
+      <c r="L4216" s="4"/>
+    </row>
+    <row r="4227" spans="11:12" x14ac:dyDescent="0.25">
       <c r="K4227" s="4"/>
-    </row>
-    <row r="4432" spans="10:15" x14ac:dyDescent="0.25">
-      <c r="J4432" s="4"/>
+      <c r="L4227" s="4"/>
+    </row>
+    <row r="4432" spans="11:16" x14ac:dyDescent="0.25">
       <c r="K4432" s="4"/>
       <c r="L4432" s="4"/>
       <c r="M4432" s="4"/>
       <c r="N4432" s="4"/>
       <c r="O4432" s="4"/>
-    </row>
-    <row r="4433" spans="10:15" x14ac:dyDescent="0.25">
-      <c r="J4433" s="4"/>
+      <c r="P4432" s="4"/>
+    </row>
+    <row r="4433" spans="11:16" x14ac:dyDescent="0.25">
       <c r="K4433" s="4"/>
       <c r="L4433" s="4"/>
       <c r="M4433" s="4"/>
       <c r="N4433" s="4"/>
       <c r="O4433" s="4"/>
-    </row>
-    <row r="4449" spans="10:11" x14ac:dyDescent="0.25">
-      <c r="J4449" s="4"/>
+      <c r="P4433" s="4"/>
+    </row>
+    <row r="4449" spans="11:12" x14ac:dyDescent="0.25">
       <c r="K4449" s="4"/>
-    </row>
-    <row r="4460" spans="10:11" x14ac:dyDescent="0.25">
-      <c r="J4460" s="4"/>
+      <c r="L4449" s="4"/>
+    </row>
+    <row r="4460" spans="11:12" x14ac:dyDescent="0.25">
       <c r="K4460" s="4"/>
-    </row>
-    <row r="4471" spans="10:11" x14ac:dyDescent="0.25">
-      <c r="J4471" s="4"/>
+      <c r="L4460" s="4"/>
+    </row>
+    <row r="4471" spans="11:12" x14ac:dyDescent="0.25">
       <c r="K4471" s="4"/>
-    </row>
-    <row r="4482" spans="10:11" x14ac:dyDescent="0.25">
-      <c r="J4482" s="4"/>
+      <c r="L4471" s="4"/>
+    </row>
+    <row r="4482" spans="11:12" x14ac:dyDescent="0.25">
       <c r="K4482" s="4"/>
-    </row>
-    <row r="4493" spans="10:11" x14ac:dyDescent="0.25">
-      <c r="J4493" s="4"/>
+      <c r="L4482" s="4"/>
+    </row>
+    <row r="4493" spans="11:12" x14ac:dyDescent="0.25">
       <c r="K4493" s="4"/>
-    </row>
-    <row r="4504" spans="10:11" x14ac:dyDescent="0.25">
-      <c r="J4504" s="4"/>
+      <c r="L4493" s="4"/>
+    </row>
+    <row r="4504" spans="11:12" x14ac:dyDescent="0.25">
       <c r="K4504" s="4"/>
-    </row>
-    <row r="4515" spans="10:11" x14ac:dyDescent="0.25">
-      <c r="J4515" s="4"/>
+      <c r="L4504" s="4"/>
+    </row>
+    <row r="4515" spans="11:12" x14ac:dyDescent="0.25">
       <c r="K4515" s="4"/>
-    </row>
-    <row r="4537" spans="10:11" x14ac:dyDescent="0.25">
-      <c r="J4537" s="4"/>
+      <c r="L4515" s="4"/>
+    </row>
+    <row r="4537" spans="11:12" x14ac:dyDescent="0.25">
       <c r="K4537" s="4"/>
-    </row>
-    <row r="4680" spans="10:11" x14ac:dyDescent="0.25">
-      <c r="J4680" s="4"/>
+      <c r="L4537" s="4"/>
+    </row>
+    <row r="4680" spans="11:12" x14ac:dyDescent="0.25">
       <c r="K4680" s="4"/>
-    </row>
-    <row r="4691" spans="10:11" x14ac:dyDescent="0.25">
-      <c r="J4691" s="4"/>
+      <c r="L4680" s="4"/>
+    </row>
+    <row r="4691" spans="11:12" x14ac:dyDescent="0.25">
       <c r="K4691" s="4"/>
-    </row>
-    <row r="4809" spans="12:15" x14ac:dyDescent="0.25">
-      <c r="L4809" s="4"/>
+      <c r="L4691" s="4"/>
+    </row>
+    <row r="4809" spans="13:16" x14ac:dyDescent="0.25">
       <c r="M4809" s="4"/>
       <c r="N4809" s="4"/>
       <c r="O4809" s="4"/>
-    </row>
-    <row r="4907" spans="10:11" x14ac:dyDescent="0.25">
-      <c r="J4907" s="4"/>
+      <c r="P4809" s="4"/>
+    </row>
+    <row r="4907" spans="11:12" x14ac:dyDescent="0.25">
       <c r="K4907" s="4"/>
-    </row>
-    <row r="4913" spans="10:11" x14ac:dyDescent="0.25">
-      <c r="K4913" s="4"/>
-    </row>
-    <row r="4925" spans="10:11" x14ac:dyDescent="0.25">
-      <c r="J4925" s="4"/>
+      <c r="L4907" s="4"/>
+    </row>
+    <row r="4913" spans="11:12" x14ac:dyDescent="0.25">
+      <c r="L4913" s="4"/>
+    </row>
+    <row r="4925" spans="11:12" x14ac:dyDescent="0.25">
       <c r="K4925" s="4"/>
-    </row>
-    <row r="4931" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K4931" s="4"/>
-    </row>
-    <row r="5429" spans="10:11" x14ac:dyDescent="0.25">
-      <c r="J5429" s="4"/>
+      <c r="L4925" s="4"/>
+    </row>
+    <row r="4931" spans="12:12" x14ac:dyDescent="0.25">
+      <c r="L4931" s="4"/>
+    </row>
+    <row r="5429" spans="11:12" x14ac:dyDescent="0.25">
       <c r="K5429" s="4"/>
-    </row>
-    <row r="5430" spans="10:11" x14ac:dyDescent="0.25">
-      <c r="J5430" s="4"/>
+      <c r="L5429" s="4"/>
+    </row>
+    <row r="5430" spans="11:12" x14ac:dyDescent="0.25">
       <c r="K5430" s="4"/>
-    </row>
-    <row r="5432" spans="10:11" x14ac:dyDescent="0.25">
-      <c r="J5432" s="4"/>
+      <c r="L5430" s="4"/>
+    </row>
+    <row r="5432" spans="11:12" x14ac:dyDescent="0.25">
       <c r="K5432" s="4"/>
-    </row>
-    <row r="5433" spans="10:11" x14ac:dyDescent="0.25">
-      <c r="J5433" s="4"/>
+      <c r="L5432" s="4"/>
+    </row>
+    <row r="5433" spans="11:12" x14ac:dyDescent="0.25">
       <c r="K5433" s="4"/>
-    </row>
-    <row r="5435" spans="10:11" x14ac:dyDescent="0.25">
-      <c r="J5435" s="4"/>
+      <c r="L5433" s="4"/>
+    </row>
+    <row r="5435" spans="11:12" x14ac:dyDescent="0.25">
       <c r="K5435" s="4"/>
-    </row>
-    <row r="5436" spans="10:11" x14ac:dyDescent="0.25">
-      <c r="J5436" s="4"/>
+      <c r="L5435" s="4"/>
+    </row>
+    <row r="5436" spans="11:12" x14ac:dyDescent="0.25">
       <c r="K5436" s="4"/>
-    </row>
-    <row r="5437" spans="10:11" x14ac:dyDescent="0.25">
-      <c r="K5437" s="4"/>
-    </row>
-    <row r="5489" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K5489" s="4"/>
-    </row>
-    <row r="5495" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K5495" s="4"/>
-    </row>
-    <row r="5609" spans="10:11" x14ac:dyDescent="0.25">
-      <c r="J5609" s="4"/>
+      <c r="L5436" s="4"/>
+    </row>
+    <row r="5437" spans="11:12" x14ac:dyDescent="0.25">
+      <c r="L5437" s="4"/>
+    </row>
+    <row r="5489" spans="12:12" x14ac:dyDescent="0.25">
+      <c r="L5489" s="4"/>
+    </row>
+    <row r="5495" spans="12:12" x14ac:dyDescent="0.25">
+      <c r="L5495" s="4"/>
+    </row>
+    <row r="5609" spans="11:12" x14ac:dyDescent="0.25">
       <c r="K5609" s="4"/>
-    </row>
-    <row r="5610" spans="10:11" x14ac:dyDescent="0.25">
-      <c r="J5610" s="4"/>
+      <c r="L5609" s="4"/>
+    </row>
+    <row r="5610" spans="11:12" x14ac:dyDescent="0.25">
       <c r="K5610" s="4"/>
-    </row>
-    <row r="5611" spans="10:11" x14ac:dyDescent="0.25">
-      <c r="J5611" s="4"/>
+      <c r="L5610" s="4"/>
+    </row>
+    <row r="5611" spans="11:12" x14ac:dyDescent="0.25">
       <c r="K5611" s="4"/>
-    </row>
-    <row r="5612" spans="10:11" x14ac:dyDescent="0.25">
-      <c r="J5612" s="4"/>
+      <c r="L5611" s="4"/>
+    </row>
+    <row r="5612" spans="11:12" x14ac:dyDescent="0.25">
       <c r="K5612" s="4"/>
-    </row>
-    <row r="5613" spans="10:11" x14ac:dyDescent="0.25">
-      <c r="J5613" s="4"/>
+      <c r="L5612" s="4"/>
+    </row>
+    <row r="5613" spans="11:12" x14ac:dyDescent="0.25">
       <c r="K5613" s="4"/>
-    </row>
-    <row r="5614" spans="10:11" x14ac:dyDescent="0.25">
-      <c r="J5614" s="4"/>
+      <c r="L5613" s="4"/>
+    </row>
+    <row r="5614" spans="11:12" x14ac:dyDescent="0.25">
       <c r="K5614" s="4"/>
-    </row>
-    <row r="5615" spans="10:11" x14ac:dyDescent="0.25">
-      <c r="J5615" s="4"/>
+      <c r="L5614" s="4"/>
+    </row>
+    <row r="5615" spans="11:12" x14ac:dyDescent="0.25">
       <c r="K5615" s="4"/>
-    </row>
-    <row r="5616" spans="10:11" x14ac:dyDescent="0.25">
-      <c r="J5616" s="4"/>
+      <c r="L5615" s="4"/>
+    </row>
+    <row r="5616" spans="11:12" x14ac:dyDescent="0.25">
       <c r="K5616" s="4"/>
-    </row>
-    <row r="5617" spans="10:11" x14ac:dyDescent="0.25">
-      <c r="J5617" s="4"/>
+      <c r="L5616" s="4"/>
+    </row>
+    <row r="5617" spans="11:12" x14ac:dyDescent="0.25">
       <c r="K5617" s="4"/>
-    </row>
-    <row r="5618" spans="10:11" x14ac:dyDescent="0.25">
-      <c r="J5618" s="4"/>
+      <c r="L5617" s="4"/>
+    </row>
+    <row r="5618" spans="11:12" x14ac:dyDescent="0.25">
       <c r="K5618" s="4"/>
-    </row>
-    <row r="5669" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K5669" s="4"/>
-    </row>
-    <row r="5670" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K5670" s="4"/>
-    </row>
-    <row r="5672" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K5672" s="4"/>
-    </row>
-    <row r="5673" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K5673" s="4"/>
-    </row>
-    <row r="5675" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K5675" s="4"/>
-    </row>
-    <row r="5676" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K5676" s="4"/>
-    </row>
-    <row r="11091" spans="10:11" x14ac:dyDescent="0.25">
-      <c r="J11091" s="4"/>
+      <c r="L5618" s="4"/>
+    </row>
+    <row r="5669" spans="12:12" x14ac:dyDescent="0.25">
+      <c r="L5669" s="4"/>
+    </row>
+    <row r="5670" spans="12:12" x14ac:dyDescent="0.25">
+      <c r="L5670" s="4"/>
+    </row>
+    <row r="5672" spans="12:12" x14ac:dyDescent="0.25">
+      <c r="L5672" s="4"/>
+    </row>
+    <row r="5673" spans="12:12" x14ac:dyDescent="0.25">
+      <c r="L5673" s="4"/>
+    </row>
+    <row r="5675" spans="12:12" x14ac:dyDescent="0.25">
+      <c r="L5675" s="4"/>
+    </row>
+    <row r="5676" spans="12:12" x14ac:dyDescent="0.25">
+      <c r="L5676" s="4"/>
+    </row>
+    <row r="11091" spans="11:12" x14ac:dyDescent="0.25">
       <c r="K11091" s="4"/>
-    </row>
-    <row r="11092" spans="10:11" x14ac:dyDescent="0.25">
-      <c r="J11092" s="4"/>
+      <c r="L11091" s="4"/>
+    </row>
+    <row r="11092" spans="11:12" x14ac:dyDescent="0.25">
       <c r="K11092" s="4"/>
-    </row>
-    <row r="11499" spans="10:11" x14ac:dyDescent="0.25">
-      <c r="J11499" s="4"/>
+      <c r="L11092" s="4"/>
+    </row>
+    <row r="11499" spans="11:12" x14ac:dyDescent="0.25">
       <c r="K11499" s="4"/>
-    </row>
-    <row r="11585" spans="10:11" x14ac:dyDescent="0.25">
-      <c r="J11585" s="4"/>
+      <c r="L11499" s="4"/>
+    </row>
+    <row r="11585" spans="11:12" x14ac:dyDescent="0.25">
       <c r="K11585" s="4"/>
-    </row>
-    <row r="11586" spans="10:11" x14ac:dyDescent="0.25">
-      <c r="J11586" s="4"/>
+      <c r="L11585" s="4"/>
+    </row>
+    <row r="11586" spans="11:12" x14ac:dyDescent="0.25">
       <c r="K11586" s="4"/>
-    </row>
-    <row r="11587" spans="10:11" x14ac:dyDescent="0.25">
-      <c r="J11587" s="4"/>
+      <c r="L11586" s="4"/>
+    </row>
+    <row r="11587" spans="11:12" x14ac:dyDescent="0.25">
       <c r="K11587" s="4"/>
-    </row>
-    <row r="11588" spans="10:11" x14ac:dyDescent="0.25">
-      <c r="J11588" s="4"/>
+      <c r="L11587" s="4"/>
+    </row>
+    <row r="11588" spans="11:12" x14ac:dyDescent="0.25">
       <c r="K11588" s="4"/>
-    </row>
-    <row r="11589" spans="10:11" x14ac:dyDescent="0.25">
-      <c r="J11589" s="4"/>
+      <c r="L11588" s="4"/>
+    </row>
+    <row r="11589" spans="11:12" x14ac:dyDescent="0.25">
       <c r="K11589" s="4"/>
-    </row>
-    <row r="11590" spans="10:11" x14ac:dyDescent="0.25">
-      <c r="J11590" s="4"/>
+      <c r="L11589" s="4"/>
+    </row>
+    <row r="11590" spans="11:12" x14ac:dyDescent="0.25">
       <c r="K11590" s="4"/>
-    </row>
-    <row r="14009" spans="10:11" x14ac:dyDescent="0.25">
-      <c r="J14009" s="4"/>
+      <c r="L11590" s="4"/>
+    </row>
+    <row r="14009" spans="11:12" x14ac:dyDescent="0.25">
       <c r="K14009" s="4"/>
-    </row>
-    <row r="14241" spans="10:11" x14ac:dyDescent="0.25">
-      <c r="J14241" s="4"/>
+      <c r="L14009" s="4"/>
+    </row>
+    <row r="14241" spans="11:12" x14ac:dyDescent="0.25">
       <c r="K14241" s="4"/>
-    </row>
-    <row r="17190" spans="10:11" x14ac:dyDescent="0.25">
-      <c r="J17190" s="4"/>
+      <c r="L14241" s="4"/>
+    </row>
+    <row r="17190" spans="11:12" x14ac:dyDescent="0.25">
       <c r="K17190" s="4"/>
-    </row>
-    <row r="17248" spans="10:11" x14ac:dyDescent="0.25">
-      <c r="J17248" s="4"/>
+      <c r="L17190" s="4"/>
+    </row>
+    <row r="17248" spans="11:12" x14ac:dyDescent="0.25">
       <c r="K17248" s="4"/>
-    </row>
-    <row r="17334" spans="10:11" x14ac:dyDescent="0.25">
-      <c r="J17334" s="4"/>
+      <c r="L17248" s="4"/>
+    </row>
+    <row r="17334" spans="11:12" x14ac:dyDescent="0.25">
       <c r="K17334" s="4"/>
-    </row>
-    <row r="17335" spans="10:11" x14ac:dyDescent="0.25">
-      <c r="J17335" s="4"/>
+      <c r="L17334" s="4"/>
+    </row>
+    <row r="17335" spans="11:12" x14ac:dyDescent="0.25">
       <c r="K17335" s="4"/>
-    </row>
-    <row r="17336" spans="10:11" x14ac:dyDescent="0.25">
-      <c r="J17336" s="4"/>
+      <c r="L17335" s="4"/>
+    </row>
+    <row r="17336" spans="11:12" x14ac:dyDescent="0.25">
       <c r="K17336" s="4"/>
-    </row>
-    <row r="17337" spans="10:11" x14ac:dyDescent="0.25">
-      <c r="J17337" s="4"/>
+      <c r="L17336" s="4"/>
+    </row>
+    <row r="17337" spans="11:12" x14ac:dyDescent="0.25">
       <c r="K17337" s="4"/>
-    </row>
-    <row r="17339" spans="10:11" x14ac:dyDescent="0.25">
-      <c r="J17339" s="4"/>
+      <c r="L17337" s="4"/>
+    </row>
+    <row r="17339" spans="11:12" x14ac:dyDescent="0.25">
       <c r="K17339" s="4"/>
+      <c r="L17339" s="4"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O17397" xr:uid="{49FDA544-07CD-40FE-921C-A333DF3D4537}"/>
+  <autoFilter ref="A1:P17397" xr:uid="{49FDA544-07CD-40FE-921C-A333DF3D4537}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -1362,17 +1369,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="21b80f9f-7b80-4525-a58f-79b685f26f5a">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="5f2cdac8-9a07-4999-a4b4-77dc96e1df04" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100AEB824E451527A4AB060B4F894264692" ma:contentTypeVersion="14" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="24a59d3ce3015b13823690cfcc9253e9">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="21b80f9f-7b80-4525-a58f-79b685f26f5a" xmlns:ns3="5f2cdac8-9a07-4999-a4b4-77dc96e1df04" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="a5a00bbc5ca9b851f6a7599a2fb545f1" ns2:_="" ns3:_="">
     <xsd:import namespace="21b80f9f-7b80-4525-a58f-79b685f26f5a"/>
@@ -1587,6 +1583,17 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="21b80f9f-7b80-4525-a58f-79b685f26f5a">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="5f2cdac8-9a07-4999-a4b4-77dc96e1df04" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0AABE7ED-FE0D-47FD-909E-696A62434AC5}">
   <ds:schemaRefs>
@@ -1596,17 +1603,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0028D6CA-8544-4F05-8674-C223B1769155}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="21b80f9f-7b80-4525-a58f-79b685f26f5a"/>
-    <ds:schemaRef ds:uri="5f2cdac8-9a07-4999-a4b4-77dc96e1df04"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2994706C-E50C-4E59-8084-BC1E19493A67}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -1623,4 +1619,15 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0028D6CA-8544-4F05-8674-C223B1769155}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="21b80f9f-7b80-4525-a58f-79b685f26f5a"/>
+    <ds:schemaRef ds:uri="5f2cdac8-9a07-4999-a4b4-77dc96e1df04"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>